--- a/docs/oc-regiones/suministro-de-combustibles/magallanes.xlsx
+++ b/docs/oc-regiones/suministro-de-combustibles/magallanes.xlsx
@@ -562,7 +562,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1992,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2057,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2122,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2187,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2252,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2317,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2382,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2447,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2512,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2577,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2642,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2707,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2772,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2837,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2902,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2967,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3032,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3097,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3162,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3227,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3292,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3357,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3422,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3487,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3552,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3617,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3682,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3747,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3812,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3877,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3942,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +4007,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4072,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4137,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4202,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4267,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4332,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4397,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4462,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4527,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4592,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4657,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4722,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4787,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4852,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4917,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4982,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5047,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5112,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5177,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5242,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5307,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5372,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5437,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5502,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5567,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5632,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5697,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5762,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5827,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5892,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5957,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +6022,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6087,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6152,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6217,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6282,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6347,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6412,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6477,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6542,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6607,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6672,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6737,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6802,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6867,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6932,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6997,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +7062,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7127,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7192,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7257,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7322,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7387,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7452,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7517,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7582,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7647,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7712,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7777,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7842,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7907,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7972,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +8037,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +8102,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8167,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8232,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8297,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8362,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8427,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8492,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8557,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8622,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8687,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8752,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8817,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8882,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8947,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +9012,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +9077,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +9142,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9207,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9272,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9337,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9402,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9467,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9532,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9597,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9662,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9727,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9792,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9857,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9922,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9987,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +10052,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +10117,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +10182,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10247,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10312,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10377,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10442,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10507,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10572,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10637,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10702,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10767,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10832,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10897,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10962,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +11027,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +11092,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +11157,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +11222,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11287,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +11352,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11417,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11482,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11547,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11612,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11677,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11742,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11807,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11872,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11937,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +12002,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +12067,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +12132,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +12197,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +12262,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +12327,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12392,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12457,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12522,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12587,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12652,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12717,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12782,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12847,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12912,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12977,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +13042,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +13107,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +13172,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +13237,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +13302,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +13367,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +13432,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13497,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12762,7 +13562,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13627,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13692,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13757,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13822,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13887,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13952,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +14017,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +14082,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +14147,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +14212,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +14277,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +14342,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +14407,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +14472,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14537,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14602,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14667,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14732,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14797,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14862,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14927,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14992,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +15057,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +15122,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +15187,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +15252,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +15317,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +15382,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +15447,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15512,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15577,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15642,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15707,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15772,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15837,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15902,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15967,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +16032,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +16097,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +16162,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +16227,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +16292,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +16357,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +16422,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +16487,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16552,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16617,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16682,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16747,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15812,7 +16812,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16877,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16942,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +17007,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +17072,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +17137,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +17202,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +17267,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +17332,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +17397,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +17462,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +17527,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17592,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +17657,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17722,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17787,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17852,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17917,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17982,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +18047,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +18112,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +18177,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +18242,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17280,7 +18372,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17341,7 +18437,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17402,7 +18502,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17463,7 +18567,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17524,7 +18632,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17585,7 +18697,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17646,7 +18762,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17707,7 +18827,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17768,7 +18892,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17829,7 +18957,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17890,7 +19022,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17951,7 +19087,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18012,7 +19152,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18073,7 +19217,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18134,7 +19282,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18195,7 +19347,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18256,7 +19412,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18317,7 +19477,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18378,7 +19542,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18439,7 +19607,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18500,7 +19672,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18561,7 +19737,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18622,7 +19802,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18683,7 +19867,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18744,7 +19932,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18805,7 +19997,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18866,7 +20062,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18927,7 +20127,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18988,7 +20192,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19049,7 +20257,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19110,7 +20322,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19171,7 +20387,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19232,7 +20452,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19293,7 +20517,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19354,7 +20582,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19415,7 +20647,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19476,7 +20712,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19537,7 +20777,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19598,7 +20842,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19659,7 +20907,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19720,7 +20972,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19781,7 +21037,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19842,7 +21102,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19903,7 +21167,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19964,7 +21232,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20025,7 +21297,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20086,7 +21362,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20147,7 +21427,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20208,7 +21492,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20269,7 +21557,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20330,7 +21622,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20391,7 +21687,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20452,7 +21752,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20513,7 +21817,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20574,7 +21882,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20635,7 +21947,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20696,7 +22012,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20757,7 +22077,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20818,7 +22142,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20879,7 +22207,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20940,7 +22272,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21001,7 +22337,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21062,7 +22402,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21123,7 +22467,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21184,7 +22532,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21245,7 +22597,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21306,7 +22662,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21367,7 +22727,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21428,7 +22792,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21489,7 +22857,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21550,7 +22922,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21611,7 +22987,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21672,7 +23052,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21733,7 +23117,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21794,7 +23182,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21855,7 +23247,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21916,7 +23312,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21977,7 +23377,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22038,7 +23442,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22099,7 +23507,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/suministro-de-combustibles/magallanes.xlsx
+++ b/docs/oc-regiones/suministro-de-combustibles/magallanes.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M355"/>
+  <dimension ref="A1:M363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2529,7 +2529,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3617-23-CM25</t>
+          <t>517903-3-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2554,12 +2554,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.114.000-2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>ESTADO MAYOR CONJUNTO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2569,17 +2569,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>2122.03</v>
+        <v>3136.01</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>517903-3-CM25</t>
+          <t>2663-40-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.114.000-2</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>ESTADO MAYOR CONJUNTO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2634,17 +2634,17 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>3136.01</v>
+        <v>4076.81</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2663-40-CM25</t>
+          <t>3617-23-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2718,7 +2718,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>4076.81</v>
+        <v>2122.03</v>
       </c>
     </row>
     <row r="36">
@@ -4284,7 +4284,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>920802-37-CM25</t>
+          <t>683-11-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4304,17 +4304,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>65.119.695-7</t>
+          <t>61.402.008-3</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4343,13 +4343,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>2225.89</v>
+        <v>2280.18</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>683-11-CM25</t>
+          <t>920802-37-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.402.008-3</t>
+          <t>65.119.695-7</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>2280.18</v>
+        <v>2225.89</v>
       </c>
     </row>
     <row r="62">
@@ -5909,7 +5909,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1540-1295-CM25</t>
+          <t>2663-248-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5949,17 +5949,17 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5968,13 +5968,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2196.08</v>
+        <v>5321.13</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2663-248-CM25</t>
+          <t>1540-1295-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6014,17 +6014,17 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6033,13 +6033,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>5321.13</v>
+        <v>2196.08</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1759-113-CM25</t>
+          <t>4589-288-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6064,12 +6064,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>60.901.014-2</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6098,13 +6098,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>2204.69</v>
+        <v>2540.32</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>4589-288-CM25</t>
+          <t>4589-287-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -6163,13 +6163,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2540.32</v>
+        <v>3810.48</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4589-287-CM25</t>
+          <t>1759-113-CM25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6189,17 +6189,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>69.251.700-8</t>
+          <t>60.901.014-2</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6228,13 +6228,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>3810.48</v>
+        <v>2204.69</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>5338-669-CM25</t>
+          <t>1070-96-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6254,17 +6254,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6293,7 +6293,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>3447.02</v>
+        <v>5371.78</v>
       </c>
     </row>
     <row r="91">
@@ -6364,7 +6364,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1070-96-CM25</t>
+          <t>5338-669-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6384,17 +6384,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6423,7 +6423,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>5371.78</v>
+        <v>3447.02</v>
       </c>
     </row>
     <row r="93">
@@ -7144,7 +7144,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3166-350-CM25</t>
+          <t>1080089-487-CM25</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7164,17 +7164,17 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.102.027-9</t>
+          <t>61.607.900-k</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -7184,17 +7184,17 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7203,13 +7203,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>2205.51</v>
+        <v>3204.14</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1080089-487-CM25</t>
+          <t>3166-350-CM25</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7229,17 +7229,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.607.900-k</t>
+          <t>61.102.027-9</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -7249,17 +7249,17 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7268,7 +7268,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>3204.14</v>
+        <v>2205.51</v>
       </c>
     </row>
     <row r="106">
@@ -8509,7 +8509,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2348-1483-CM25</t>
+          <t>2348-1485-CM25</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8568,13 +8568,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>20623.45</v>
+        <v>15467.59</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2348-1485-CM25</t>
+          <t>2348-1483-CM25</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>15467.59</v>
+        <v>20623.45</v>
       </c>
     </row>
     <row r="127">
@@ -9289,7 +9289,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>764-275-CM25</t>
+          <t>1858-14-CM25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>60.511.120-3</t>
+          <t>72.443.600-5</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE MAGALLANES Y DE LA ANTÁRTICA CHILE</t>
+          <t>SERVICIO DE EVALUACION AMBIENTAL</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -9329,17 +9329,17 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -9348,7 +9348,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>2150.31</v>
+        <v>2150.41</v>
       </c>
     </row>
     <row r="138">
@@ -9419,7 +9419,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1858-14-CM25</t>
+          <t>764-275-CM25</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>72.443.600-5</t>
+          <t>60.511.120-3</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SERVICIO DE EVALUACION AMBIENTAL</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE MAGALLANES Y DE LA ANTÁRTICA CHILE</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9459,17 +9459,17 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -9478,7 +9478,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>2150.41</v>
+        <v>2150.31</v>
       </c>
     </row>
     <row r="140">
@@ -10264,7 +10264,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2348-1556-CM25</t>
+          <t>1057402-36781-CM25</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -10289,12 +10289,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>69.250.200-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -10323,13 +10323,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>15574.87</v>
+        <v>2157.59</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1057402-36781-CM25</t>
+          <t>2348-1556-CM25</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>69.250.200-0</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -10388,7 +10388,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>2157.59</v>
+        <v>15574.87</v>
       </c>
     </row>
     <row r="154">
@@ -10524,7 +10524,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>4890-250-CM25</t>
+          <t>3704-327-CM25</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>61.972.500-k</t>
+          <t>69.254.400-5</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>Ilustre Municipalidad de Cabo de Hornos</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>2200.4</v>
+        <v>6285.63</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>3704-327-CM25</t>
+          <t>2663-508-CM25</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10614,12 +10614,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>69.254.400-5</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabo de Hornos</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10629,17 +10629,17 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -10648,13 +10648,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>6285.63</v>
+        <v>5239.06</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2663-508-CM25</t>
+          <t>4890-250-CM25</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>61.972.500-k</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10694,17 +10694,17 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -10713,7 +10713,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>5239.06</v>
+        <v>2200.4</v>
       </c>
     </row>
     <row r="159">
@@ -12084,7 +12084,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1965-727-CM25</t>
+          <t>1759-462-CM25</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>61.004.054-3</t>
+          <t>60.901.014-2</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -12143,13 +12143,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>4267.3</v>
+        <v>2225.68</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1759-462-CM25</t>
+          <t>1965-727-CM25</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -12174,12 +12174,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>60.901.014-2</t>
+          <t>61.004.054-3</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -12208,7 +12208,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>2225.68</v>
+        <v>4267.3</v>
       </c>
     </row>
     <row r="182">
@@ -12539,7 +12539,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>3617-236-CM25</t>
+          <t>661-92-CM25</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.802.012-6</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -12579,17 +12579,17 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -12598,13 +12598,13 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>5981.77</v>
+        <v>2283.95</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>661-92-CM25</t>
+          <t>1540-6591-CM25</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>61.802.012-6</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -12644,17 +12644,17 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -12663,13 +12663,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>2283.95</v>
+        <v>5887.96</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1540-6591-CM25</t>
+          <t>3617-236-CM25</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12694,12 +12694,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -12728,7 +12728,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>5887.96</v>
+        <v>5981.77</v>
       </c>
     </row>
     <row r="190">
@@ -12929,7 +12929,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2663-667-CM25</t>
+          <t>4589-594-CM25</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12954,12 +12954,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12969,17 +12969,17 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -12988,13 +12988,13 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>5482.28</v>
+        <v>2609.56</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>4589-594-CM25</t>
+          <t>2663-667-CM25</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -13019,12 +13019,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>69.251.700-8</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -13034,17 +13034,17 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -13053,7 +13053,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>2609.56</v>
+        <v>5482.28</v>
       </c>
     </row>
     <row r="195">
@@ -13124,7 +13124,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>3617-259-CM25</t>
+          <t>1759-511-CM25</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -13149,12 +13149,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.901.014-2</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -13164,17 +13164,17 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -13183,13 +13183,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>2298.25</v>
+        <v>2517.13</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1759-511-CM25</t>
+          <t>3617-259-CM25</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -13214,12 +13214,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>60.901.014-2</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -13229,17 +13229,17 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -13248,7 +13248,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>2517.13</v>
+        <v>2298.25</v>
       </c>
     </row>
     <row r="198">
@@ -14814,7 +14814,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1540-186-CM26</t>
+          <t>1057402-787-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -14839,12 +14839,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14854,17 +14854,17 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -14873,13 +14873,13 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>2385.53</v>
+        <v>2383.26</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1057402-787-CM26</t>
+          <t>1540-186-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14919,17 +14919,17 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -14938,7 +14938,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>2383.26</v>
+        <v>2385.53</v>
       </c>
     </row>
     <row r="224">
@@ -15659,7 +15659,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2663-73-CM26</t>
+          <t>4052-13-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -15684,12 +15684,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>69.251.200-6</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>I MUNICIPALIDAD DE LAGUNA BLANCA</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -15699,17 +15699,17 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -15718,13 +15718,13 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>5794.35</v>
+        <v>11588.69</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>4052-13-CM26</t>
+          <t>2663-73-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -15749,12 +15749,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>69.251.200-6</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGUNA BLANCA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -15764,17 +15764,17 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -15783,7 +15783,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>11588.69</v>
+        <v>5794.35</v>
       </c>
     </row>
     <row r="237">
@@ -15919,7 +15919,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1233613-242-CM26</t>
+          <t>1536-42-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15944,12 +15944,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>61.980.960-2</t>
+          <t>60.511.123-8</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Magallanes</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15978,13 +15978,13 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>11530.17</v>
+        <v>2536.64</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1536-42-CM26</t>
+          <t>1233613-242-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -16009,12 +16009,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>60.511.123-8</t>
+          <t>61.980.960-2</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
+          <t>Servicio Local de Educación Pública Magallanes</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -16043,13 +16043,13 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>2536.64</v>
+        <v>11530.17</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1988-7-CM26</t>
+          <t>1988-8-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -16108,13 +16108,13 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>2435.14</v>
+        <v>3498.22</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1988-8-CM26</t>
+          <t>1988-7-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -16173,7 +16173,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>3498.22</v>
+        <v>2435.14</v>
       </c>
     </row>
     <row r="243">
@@ -16244,7 +16244,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1540-600-CM26</t>
+          <t>2663-107-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -16269,12 +16269,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -16284,17 +16284,17 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -16303,13 +16303,13 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>8602.01</v>
+        <v>5585.72</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2663-107-CM26</t>
+          <t>1540-600-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -16334,12 +16334,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -16349,17 +16349,17 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>5585.72</v>
+        <v>8602.01</v>
       </c>
     </row>
     <row r="246">
@@ -16569,7 +16569,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>4589-115-CM26</t>
+          <t>4589-116-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -16634,7 +16634,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>4589-116-CM26</t>
+          <t>4589-115-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -17544,7 +17544,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2348-169-CM26</t>
+          <t>2348-170-CM26</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -17603,13 +17603,13 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>9402.17</v>
+        <v>8461.959999999999</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2348-170-CM26</t>
+          <t>2348-169-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -17668,7 +17668,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>8461.959999999999</v>
+        <v>9402.17</v>
       </c>
     </row>
     <row r="266">
@@ -17934,7 +17934,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>1965-186-CM26</t>
+          <t>2663-206-CM26</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -17959,12 +17959,12 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>61.004.054-3</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -17974,17 +17974,17 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -17993,13 +17993,13 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>2353.79</v>
+        <v>8966.799999999999</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1965-187-CM26</t>
+          <t>1965-186-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -18058,7 +18058,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>4371.32</v>
+        <v>2353.79</v>
       </c>
     </row>
     <row r="272">
@@ -18129,7 +18129,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2663-206-CM26</t>
+          <t>1965-187-CM26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -18154,12 +18154,12 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>61.004.054-3</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -18169,17 +18169,17 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -18188,13 +18188,13 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>8966.799999999999</v>
+        <v>4371.32</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2348-195-CM26</t>
+          <t>3704-110-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -18219,12 +18219,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>69.250.200-0</t>
+          <t>69.254.400-5</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+          <t>Ilustre Municipalidad de Cabo de Hornos</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -18234,17 +18234,17 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -18253,13 +18253,13 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>15624.48</v>
+        <v>2901.69</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2348-200-CM26</t>
+          <t>1038-75-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -18279,17 +18279,17 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>69.250.200-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -18299,17 +18299,17 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -18318,13 +18318,13 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>191564.92</v>
+        <v>5580.17</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>1038-75-CM26</t>
+          <t>2348-200-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -18344,17 +18344,17 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.250.200-0</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -18364,17 +18364,17 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -18383,13 +18383,13 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>5580.17</v>
+        <v>191564.92</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>3704-110-CM26</t>
+          <t>2348-195-CM26</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -18414,12 +18414,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>69.254.400-5</t>
+          <t>69.250.200-0</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabo de Hornos</t>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -18429,17 +18429,17 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -18448,7 +18448,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>2901.69</v>
+        <v>15624.48</v>
       </c>
     </row>
     <row r="278">
@@ -18714,7 +18714,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>1239966-171-CM26</t>
+          <t>1162-70-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -18739,12 +18739,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>71.165.800-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Corporación de Ecuación, Salud y Menores de Puerto Natales</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -18773,13 +18773,13 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>2460.16</v>
+        <v>23243.75</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>1162-70-CM26</t>
+          <t>1239966-171-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -18804,12 +18804,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>71.165.800-9</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>Corporación de Ecuación, Salud y Menores de Puerto Natales</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -18838,7 +18838,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>23243.75</v>
+        <v>2460.16</v>
       </c>
     </row>
     <row r="284">
@@ -18974,7 +18974,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>764-95-CM26</t>
+          <t>2074-13-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -18999,12 +18999,12 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>60.511.120-3</t>
+          <t>60.902.072-5</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE MAGALLANES Y DE LA ANTÁRTICA CHILE</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -19033,13 +19033,13 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>3333.67</v>
+        <v>2354.16</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2074-13-CM26</t>
+          <t>764-95-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -19064,12 +19064,12 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>60.902.072-5</t>
+          <t>60.511.120-3</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE MAGALLANES Y DE LA ANTÁRTICA CHILE</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -19098,7 +19098,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>2354.16</v>
+        <v>3333.67</v>
       </c>
     </row>
     <row r="288">
@@ -19364,7 +19364,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2663-304-CM26</t>
+          <t>3617-78-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -19389,12 +19389,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -19404,17 +19404,17 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
@@ -19423,13 +19423,13 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>8940.65</v>
+        <v>2476.97</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>3617-78-CM26</t>
+          <t>2663-304-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -19454,12 +19454,12 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -19469,17 +19469,17 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
@@ -19488,7 +19488,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>2476.97</v>
+        <v>8940.65</v>
       </c>
     </row>
     <row r="294">
@@ -19819,7 +19819,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>5338-329-CM26</t>
+          <t>3617-83-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -19844,12 +19844,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -19878,13 +19878,13 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>2988.21</v>
+        <v>6547.43</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>3617-83-CM26</t>
+          <t>5338-329-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19909,12 +19909,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -19943,7 +19943,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>6547.43</v>
+        <v>2988.21</v>
       </c>
     </row>
     <row r="301">
@@ -20534,7 +20534,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>638-96-CM26</t>
+          <t>1540-1503-CM26</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -20559,12 +20559,12 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>61.824.000-2</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>SERVIU REGION DE MAGALLANES Y DE LA ANTARTICA CHILENA</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -20593,13 +20593,13 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>2318.43</v>
+        <v>9165.9</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>1540-1503-CM26</t>
+          <t>638-96-CM26</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -20624,12 +20624,12 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.824.000-2</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>SERVIU REGION DE MAGALLANES Y DE LA ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -20658,7 +20658,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>9165.9</v>
+        <v>2318.43</v>
       </c>
     </row>
     <row r="312">
@@ -20729,7 +20729,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2348-296-CM26</t>
+          <t>2348-298-CM26</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -20788,13 +20788,13 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>8087.47</v>
+        <v>12939.96</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2348-298-CM26</t>
+          <t>2348-296-CM26</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -20853,13 +20853,13 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>12939.96</v>
+        <v>8087.47</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>3866-78-CM26</t>
+          <t>1239966-281-CM26</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -20884,12 +20884,12 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>69.251.300-2</t>
+          <t>71.165.800-9</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
+          <t>Corporación de Ecuación, Salud y Menores de Puerto Natales</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -20899,17 +20899,17 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
@@ -20918,13 +20918,13 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>10687.07</v>
+        <v>2297.72</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>1239966-281-CM26</t>
+          <t>3866-78-CM26</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -20949,12 +20949,12 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>71.165.800-9</t>
+          <t>69.251.300-2</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Corporación de Ecuación, Salud y Menores de Puerto Natales</t>
+          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -20964,17 +20964,17 @@
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
@@ -20983,7 +20983,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>2297.72</v>
+        <v>10687.07</v>
       </c>
     </row>
     <row r="317">
@@ -21054,7 +21054,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>1057402-7542-CM26</t>
+          <t>855-111-CM26</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -21074,17 +21074,17 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -21113,13 +21113,13 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>6944.15</v>
+        <v>2314.14</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>855-111-CM26</t>
+          <t>1057402-7542-CM26</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -21139,17 +21139,17 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -21178,7 +21178,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>2314.14</v>
+        <v>6944.15</v>
       </c>
     </row>
     <row r="320">
@@ -21379,7 +21379,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>3617-93-CM26</t>
+          <t>2663-456-CM26</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -21404,12 +21404,12 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -21419,17 +21419,17 @@
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
@@ -21438,13 +21438,13 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>16986.4</v>
+        <v>8493.200000000001</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2663-456-CM26</t>
+          <t>3617-93-CM26</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -21469,12 +21469,12 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -21484,17 +21484,17 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
@@ -21503,7 +21503,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>8493.200000000001</v>
+        <v>16986.4</v>
       </c>
     </row>
     <row r="325">
@@ -21574,7 +21574,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>764-172-CM26</t>
+          <t>4589-363-CM26</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -21594,17 +21594,17 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>60.511.120-3</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE MAGALLANES Y DE LA ANTÁRTICA CHILE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -21633,13 +21633,13 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>2346.39</v>
+        <v>2728.36</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>4589-363-CM26</t>
+          <t>4589-364-CM26</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -21704,7 +21704,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>4589-364-CM26</t>
+          <t>764-172-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -21724,17 +21724,17 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>69.251.700-8</t>
+          <t>60.511.120-3</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE MAGALLANES Y DE LA ANTÁRTICA CHILE</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -21763,7 +21763,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>2728.36</v>
+        <v>2346.39</v>
       </c>
     </row>
     <row r="329">
@@ -22029,7 +22029,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>1490610-10-CM26</t>
+          <t>1988-44-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -22054,12 +22054,12 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>60.701.003-K</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -22088,13 +22088,13 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>24489.71</v>
+        <v>5388.84</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>1988-44-CM26</t>
+          <t>2663-504-CM26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>60.701.003-K</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -22134,17 +22134,17 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
@@ -22153,13 +22153,13 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>5388.84</v>
+        <v>8760.4</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2663-504-CM26</t>
+          <t>1490610-10-CM26</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -22184,12 +22184,12 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -22199,17 +22199,17 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
@@ -22218,13 +22218,13 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>8760.4</v>
+        <v>24489.71</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>1080094-168-CM26</t>
+          <t>3704-241-CM26</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -22249,12 +22249,12 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>61.607.900-k</t>
+          <t>69.254.400-5</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>Ilustre Municipalidad de Cabo de Hornos</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -22264,17 +22264,17 @@
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
@@ -22283,13 +22283,13 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>2354.49</v>
+        <v>8760.879999999999</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>1080094-169-CM26</t>
+          <t>1080094-168-CM26</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -22329,17 +22329,17 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
@@ -22348,13 +22348,13 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>8596.620000000001</v>
+        <v>2354.49</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>3704-241-CM26</t>
+          <t>1080094-169-CM26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -22379,12 +22379,12 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>69.254.400-5</t>
+          <t>61.607.900-k</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabo de Hornos</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -22413,7 +22413,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>8760.879999999999</v>
+        <v>8596.620000000001</v>
       </c>
     </row>
     <row r="339">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
@@ -22939,7 +22939,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>1965-503-CM26</t>
+          <t>5147-276-CM26</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -22959,17 +22959,17 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>61.004.054-3</t>
+          <t>69.251.600-1</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -22998,13 +22998,13 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>6472.91</v>
+        <v>5394.09</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>5147-276-CM26</t>
+          <t>1965-503-CM26</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -23024,17 +23024,17 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>69.251.600-1</t>
+          <t>61.004.054-3</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -23063,13 +23063,13 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>5394.09</v>
+        <v>6472.91</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>1540-2012-CM26</t>
+          <t>1536-201-CM26</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -23094,12 +23094,12 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>60.511.123-8</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -23128,13 +23128,13 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>9816.790000000001</v>
+        <v>2295.88</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>1536-201-CM26</t>
+          <t>1540-2012-CM26</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -23159,12 +23159,12 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>60.511.123-8</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -23193,7 +23193,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>2295.88</v>
+        <v>9816.790000000001</v>
       </c>
     </row>
     <row r="351">
@@ -23414,7 +23414,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
@@ -23459,7 +23459,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>1347-29-CM26</t>
+          <t>920802-135-CM26</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -23469,56 +23469,576 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>oct-2026</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>65.119.695-7</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M355" s="2" t="n">
+        <v>2261.98</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>3866-143-CM26</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F355" t="inlineStr">
-        <is>
-          <t>61.002.492-0</t>
-        </is>
-      </c>
-      <c r="G355" t="inlineStr">
-        <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
-        </is>
-      </c>
-      <c r="H355" t="inlineStr">
-        <is>
-          <t>Magallanes</t>
-        </is>
-      </c>
-      <c r="I355" t="inlineStr">
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>69.251.300-2</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
         <is>
           <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
-      <c r="J355" t="inlineStr">
+      <c r="J356" t="inlineStr">
         <is>
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr">
+      <c r="K356" t="inlineStr">
         <is>
           <t>Atacama</t>
         </is>
       </c>
-      <c r="L355" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M355" s="2" t="n">
-        <v>2227.49</v>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M356" s="2" t="n">
+        <v>14287.9</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2663-639-CM26</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>69.250.100-4</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>79.588.870-5</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M357" s="2" t="n">
+        <v>8174.86</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>1057402-10991-CM26</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>79.588.870-5</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M358" s="2" t="n">
+        <v>4386.9</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>1239966-450-CM26</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>71.165.800-9</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>Corporación de Ecuación, Salud y Menores de Puerto Natales</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M359" s="2" t="n">
+        <v>2546.73</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2004-41-CM26</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>60.103.009-8</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M360" s="2" t="n">
+        <v>4087.64</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2663-668-CM26</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>69.250.100-4</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>79.588.870-5</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M361" s="2" t="n">
+        <v>8108.82</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>707427-56-CM26</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M362" s="2" t="n">
+        <v>2229.93</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>1162-173-CM26</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M363" s="2" t="n">
+        <v>14743.65</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/suministro-de-combustibles/magallanes.xlsx
+++ b/docs/oc-regiones/suministro-de-combustibles/magallanes.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M366"/>
+  <dimension ref="A1:M368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8574,7 +8574,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2348-1485-CM25</t>
+          <t>2348-1483-CM25</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>15467.59</v>
+        <v>20623.45</v>
       </c>
     </row>
     <row r="127">
@@ -8704,7 +8704,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2348-1483-CM25</t>
+          <t>2348-1485-CM25</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8763,7 +8763,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>20623.45</v>
+        <v>15467.59</v>
       </c>
     </row>
     <row r="129">
@@ -12279,7 +12279,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1609-412-CM25</t>
+          <t>1609-413-CM25</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12338,13 +12338,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>5335.33</v>
+        <v>10670.65</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1609-413-CM25</t>
+          <t>1609-412-CM25</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>10670.65</v>
+        <v>5335.33</v>
       </c>
     </row>
     <row r="185">
@@ -12669,7 +12669,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>661-92-CM25</t>
+          <t>1540-6591-CM25</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12694,12 +12694,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>61.802.012-6</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -12709,17 +12709,17 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -12728,13 +12728,13 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>2283.95</v>
+        <v>5887.96</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1540-6591-CM25</t>
+          <t>661-92-CM25</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12759,12 +12759,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.802.012-6</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12774,17 +12774,17 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -12793,7 +12793,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>5887.96</v>
+        <v>2283.95</v>
       </c>
     </row>
     <row r="191">
@@ -12994,7 +12994,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2663-667-CM25</t>
+          <t>4589-595-CM25</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -13019,12 +13019,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -13034,17 +13034,17 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>5482.28</v>
+        <v>2609.56</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>4589-594-CM25</t>
+          <t>2663-667-CM25</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -13084,12 +13084,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>69.251.700-8</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -13099,17 +13099,17 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -13118,13 +13118,13 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>2609.56</v>
+        <v>5482.28</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>4589-595-CM25</t>
+          <t>4589-594-CM25</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -14879,7 +14879,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1540-186-CM26</t>
+          <t>1057402-787-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14919,17 +14919,17 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -14938,13 +14938,13 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>2385.53</v>
+        <v>2383.26</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1057402-787-CM26</t>
+          <t>1540-186-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14969,12 +14969,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14984,17 +14984,17 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -15003,7 +15003,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>2383.26</v>
+        <v>2385.53</v>
       </c>
     </row>
     <row r="225">
@@ -15724,7 +15724,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>4052-13-CM26</t>
+          <t>2663-73-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -15749,12 +15749,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>69.251.200-6</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGUNA BLANCA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -15764,17 +15764,17 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -15783,13 +15783,13 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>11588.69</v>
+        <v>5794.35</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2663-73-CM26</t>
+          <t>4052-13-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -15814,12 +15814,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>69.251.200-6</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>I MUNICIPALIDAD DE LAGUNA BLANCA</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -15829,17 +15829,17 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -15848,13 +15848,13 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>5794.35</v>
+        <v>11588.69</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>1237328-48-CM26</t>
+          <t>3617-44-CM26</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -15879,12 +15879,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -15894,17 +15894,17 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -15913,13 +15913,13 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>50742.1</v>
+        <v>5766.15</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>3617-44-CM26</t>
+          <t>1237328-48-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15944,12 +15944,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15959,17 +15959,17 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -15978,13 +15978,13 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>5766.15</v>
+        <v>50742.1</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1536-42-CM26</t>
+          <t>1233613-229-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -16004,17 +16004,17 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>60.511.123-8</t>
+          <t>61.980.960-2</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
+          <t>Servicio Local de Educación Pública Magallanes</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -16043,7 +16043,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>2536.64</v>
+        <v>10377.15</v>
       </c>
     </row>
     <row r="241">
@@ -16114,7 +16114,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1233613-229-CM26</t>
+          <t>1536-42-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -16134,17 +16134,17 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>61.980.960-2</t>
+          <t>60.511.123-8</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Magallanes</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -16173,7 +16173,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>10377.15</v>
+        <v>2536.64</v>
       </c>
     </row>
     <row r="243">
@@ -16374,7 +16374,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1540-600-CM26</t>
+          <t>2663-107-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -16399,12 +16399,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -16414,17 +16414,17 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -16433,13 +16433,13 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>8602.01</v>
+        <v>5585.72</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2663-107-CM26</t>
+          <t>1540-600-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -16464,12 +16464,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -16479,17 +16479,17 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -16498,7 +16498,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>5585.72</v>
+        <v>8602.01</v>
       </c>
     </row>
     <row r="248">
@@ -16634,7 +16634,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>4589-115-CM26</t>
+          <t>4589-116-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -16699,7 +16699,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>4589-114-CM26</t>
+          <t>4589-115-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>2663.12</v>
+        <v>3328.89</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>4589-116-CM26</t>
+          <t>4589-114-CM26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -16823,7 +16823,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>3328.89</v>
+        <v>2663.12</v>
       </c>
     </row>
     <row r="253">
@@ -17089,7 +17089,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>3637-87-CM26</t>
+          <t>1239966-109-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -17109,17 +17109,17 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>69.251.500-5</t>
+          <t>71.165.800-9</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN GREGORIO</t>
+          <t>Corporación de Ecuación, Salud y Menores de Puerto Natales</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -17129,17 +17129,17 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -17148,13 +17148,13 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>26078.07</v>
+        <v>2258.31</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>1239966-109-CM26</t>
+          <t>3637-87-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -17174,17 +17174,17 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>71.165.800-9</t>
+          <t>69.251.500-5</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Corporación de Ecuación, Salud y Menores de Puerto Natales</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN GREGORIO</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -17194,17 +17194,17 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -17213,7 +17213,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>2258.31</v>
+        <v>26078.07</v>
       </c>
     </row>
     <row r="259">
@@ -17999,7 +17999,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1965-186-CM26</t>
+          <t>2663-206-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -18024,12 +18024,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>61.004.054-3</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -18039,17 +18039,17 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -18058,13 +18058,13 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>2353.79</v>
+        <v>8966.799999999999</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>1540-1012-CM26</t>
+          <t>3704-103-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -18089,12 +18089,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>69.254.400-5</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>Ilustre Municipalidad de Cabo de Hornos</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -18123,13 +18123,13 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>8630.549999999999</v>
+        <v>7285.53</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>3704-103-CM26</t>
+          <t>1965-187-CM26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -18154,12 +18154,12 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>69.254.400-5</t>
+          <t>61.004.054-3</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabo de Hornos</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -18188,13 +18188,13 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>7285.53</v>
+        <v>4371.32</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2663-206-CM26</t>
+          <t>1965-186-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -18219,12 +18219,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>61.004.054-3</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -18234,17 +18234,17 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -18253,13 +18253,13 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>8966.799999999999</v>
+        <v>2353.79</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>1965-187-CM26</t>
+          <t>1540-1012-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -18284,12 +18284,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>61.004.054-3</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -18318,7 +18318,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>4371.32</v>
+        <v>8630.549999999999</v>
       </c>
     </row>
     <row r="276">
@@ -18454,7 +18454,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2348-195-CM26</t>
+          <t>2348-200-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -18494,17 +18494,17 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
@@ -18513,13 +18513,13 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>15624.48</v>
+        <v>191564.92</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2348-200-CM26</t>
+          <t>2348-195-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -18559,17 +18559,17 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
@@ -18578,7 +18578,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>191564.92</v>
+        <v>15624.48</v>
       </c>
     </row>
     <row r="280">
@@ -18844,7 +18844,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>1162-70-CM26</t>
+          <t>1239966-171-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18869,12 +18869,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>71.165.800-9</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>Corporación de Ecuación, Salud y Menores de Puerto Natales</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -18903,13 +18903,13 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>23243.75</v>
+        <v>2460.16</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>1239966-171-CM26</t>
+          <t>1162-70-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -18934,12 +18934,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>71.165.800-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Corporación de Ecuación, Salud y Menores de Puerto Natales</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -18968,13 +18968,13 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>2460.16</v>
+        <v>23243.75</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>3366-26-CM26</t>
+          <t>2663-259-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -18999,12 +18999,12 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>61.101.010-9</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -19033,13 +19033,13 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>42645.21</v>
+        <v>8889.780000000001</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2663-259-CM26</t>
+          <t>764-95-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -19064,12 +19064,12 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>60.511.120-3</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE MAGALLANES Y DE LA ANTÁRTICA CHILE</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -19098,13 +19098,13 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>8889.780000000001</v>
+        <v>3333.67</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>764-95-CM26</t>
+          <t>2074-13-CM26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -19129,12 +19129,12 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>60.511.120-3</t>
+          <t>60.902.072-5</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE MAGALLANES Y DE LA ANTÁRTICA CHILE</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -19163,13 +19163,13 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>3333.67</v>
+        <v>2354.16</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2074-13-CM26</t>
+          <t>3366-26-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -19194,12 +19194,12 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>60.902.072-5</t>
+          <t>61.101.010-9</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -19228,7 +19228,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>2354.16</v>
+        <v>42645.21</v>
       </c>
     </row>
     <row r="290">
@@ -19364,7 +19364,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>1057402-5571-CM26</t>
+          <t>1540-1232-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -19389,12 +19389,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -19404,17 +19404,17 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
@@ -19423,13 +19423,13 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>2367.35</v>
+        <v>9500.709999999999</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>1540-1232-CM26</t>
+          <t>1057402-5571-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -19454,12 +19454,12 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -19469,17 +19469,17 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
@@ -19488,7 +19488,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>9500.709999999999</v>
+        <v>2367.35</v>
       </c>
     </row>
     <row r="294">
@@ -19689,7 +19689,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>1960-43-CM26</t>
+          <t>1609-156-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -19709,17 +19709,17 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>72.229.800-4</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -19748,13 +19748,13 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>2407.86</v>
+        <v>22398.67</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>1609-156-CM26</t>
+          <t>1960-43-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -19774,17 +19774,17 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>72.229.800-4</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -19813,7 +19813,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>22398.67</v>
+        <v>2407.86</v>
       </c>
     </row>
     <row r="299">
@@ -20924,7 +20924,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2348-296-CM26</t>
+          <t>2348-298-CM26</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -20983,13 +20983,13 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>8087.47</v>
+        <v>12939.96</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2348-298-CM26</t>
+          <t>2348-296-CM26</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -21048,13 +21048,13 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>12939.96</v>
+        <v>8087.47</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>1239966-281-CM26</t>
+          <t>3866-78-CM26</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -21079,12 +21079,12 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>71.165.800-9</t>
+          <t>69.251.300-2</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Corporación de Ecuación, Salud y Menores de Puerto Natales</t>
+          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -21094,17 +21094,17 @@
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
@@ -21113,13 +21113,13 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>2297.72</v>
+        <v>10687.07</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>3866-78-CM26</t>
+          <t>1239966-281-CM26</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -21144,12 +21144,12 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>69.251.300-2</t>
+          <t>71.165.800-9</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
+          <t>Corporación de Ecuación, Salud y Menores de Puerto Natales</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -21159,17 +21159,17 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
@@ -21178,7 +21178,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>10687.07</v>
+        <v>2297.72</v>
       </c>
     </row>
     <row r="320">
@@ -21574,7 +21574,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2663-456-CM26</t>
+          <t>3617-93-CM26</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -21599,12 +21599,12 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -21614,17 +21614,17 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
@@ -21633,13 +21633,13 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>8493.200000000001</v>
+        <v>16986.4</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>3617-93-CM26</t>
+          <t>2663-456-CM26</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -21664,12 +21664,12 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -21679,17 +21679,17 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
@@ -21698,7 +21698,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>16986.4</v>
+        <v>8493.200000000001</v>
       </c>
     </row>
     <row r="328">
@@ -21769,7 +21769,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>4589-363-CM26</t>
+          <t>764-172-CM26</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -21789,17 +21789,17 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>69.251.700-8</t>
+          <t>60.511.120-3</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE MAGALLANES Y DE LA ANTÁRTICA CHILE</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -21828,13 +21828,13 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>2728.36</v>
+        <v>2346.39</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>4589-364-CM26</t>
+          <t>4589-363-CM26</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -21899,7 +21899,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>764-172-CM26</t>
+          <t>4589-364-CM26</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -21919,17 +21919,17 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>60.511.120-3</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE MAGALLANES Y DE LA ANTÁRTICA CHILE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -21958,13 +21958,13 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>2346.39</v>
+        <v>2728.36</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>3617-97-CM26</t>
+          <t>1776-57-CM26</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -21989,12 +21989,12 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.804.017-K</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -22004,17 +22004,17 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
@@ -22023,13 +22023,13 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>16404.02</v>
+        <v>5468.01</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>1776-57-CM26</t>
+          <t>3617-97-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -22054,12 +22054,12 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>60.804.017-K</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -22069,17 +22069,17 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
@@ -22088,7 +22088,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>5468.01</v>
+        <v>16404.02</v>
       </c>
     </row>
     <row r="334">
@@ -22159,7 +22159,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>1233613-1532-CM26</t>
+          <t>2663-504-CM26</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -22179,17 +22179,17 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>61.980.960-2</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Magallanes</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -22199,17 +22199,17 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
@@ -22218,7 +22218,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>16425.76</v>
+        <v>8760.4</v>
       </c>
     </row>
     <row r="336">
@@ -22289,7 +22289,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2663-504-CM26</t>
+          <t>1233613-1532-CM26</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -22309,17 +22309,17 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>61.980.960-2</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>Servicio Local de Educación Pública Magallanes</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -22329,17 +22329,17 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
@@ -22348,7 +22348,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>8760.4</v>
+        <v>16425.76</v>
       </c>
     </row>
     <row r="338">
@@ -22484,7 +22484,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>1080094-168-CM26</t>
+          <t>1080094-169-CM26</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -22524,17 +22524,17 @@
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
@@ -22543,13 +22543,13 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>2354.49</v>
+        <v>8596.620000000001</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>1080094-169-CM26</t>
+          <t>1080094-168-CM26</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -22589,17 +22589,17 @@
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
@@ -22608,7 +22608,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>8596.620000000001</v>
+        <v>2354.49</v>
       </c>
     </row>
     <row r="342">
@@ -23784,7 +23784,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2663-639-CM26</t>
+          <t>1080094-205-CM26</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -23799,7 +23799,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -23809,12 +23809,12 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>61.607.900-k</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -23824,17 +23824,17 @@
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K360" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
@@ -23843,13 +23843,13 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>8174.86</v>
+        <v>6112.41</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>1057402-10991-CM26</t>
+          <t>1080089-613-CM26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -23864,7 +23864,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -23874,12 +23874,12 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.607.900-k</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -23889,17 +23889,17 @@
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
@@ -23908,13 +23908,13 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>4386.9</v>
+        <v>3056.2</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>1239966-450-CM26</t>
+          <t>2663-639-CM26</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -23929,7 +23929,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -23939,12 +23939,12 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>71.165.800-9</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Corporación de Ecuación, Salud y Menores de Puerto Natales</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -23954,17 +23954,17 @@
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
@@ -23973,13 +23973,13 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>2546.73</v>
+        <v>8174.86</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2004-41-CM26</t>
+          <t>1057402-10991-CM26</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -23994,7 +23994,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -24004,12 +24004,12 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>60.103.009-8</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -24019,17 +24019,17 @@
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
@@ -24038,13 +24038,13 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>4087.64</v>
+        <v>4386.9</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>707427-56-CM26</t>
+          <t>1239966-450-CM26</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -24059,7 +24059,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -24069,12 +24069,12 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>71.165.800-9</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Corporación de Ecuación, Salud y Menores de Puerto Natales</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -24103,13 +24103,13 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>2229.93</v>
+        <v>2546.73</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2663-668-CM26</t>
+          <t>2004-41-CM26</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -24124,7 +24124,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -24134,12 +24134,12 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>60.103.009-8</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -24149,17 +24149,17 @@
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
@@ -24168,72 +24168,202 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>8108.82</v>
+        <v>4087.64</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
+          <t>2663-668-CM26</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>69.250.100-4</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>79.588.870-5</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M366" s="2" t="n">
+        <v>8108.82</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
           <t>1162-173-CM26</t>
         </is>
       </c>
-      <c r="B366" t="inlineStr">
+      <c r="B367" t="inlineStr">
         <is>
           <t>2239-13-LR25</t>
         </is>
       </c>
-      <c r="C366" t="inlineStr">
+      <c r="C367" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr">
+      <c r="D367" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E366" t="inlineStr">
+      <c r="E367" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F366" t="inlineStr">
+      <c r="F367" t="inlineStr">
         <is>
           <t>61.308.000-7</t>
         </is>
       </c>
-      <c r="G366" t="inlineStr">
+      <c r="G367" t="inlineStr">
         <is>
           <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
-      <c r="H366" t="inlineStr">
-        <is>
-          <t>Magallanes</t>
-        </is>
-      </c>
-      <c r="I366" t="inlineStr">
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
         <is>
           <t>COPEC S.A.</t>
         </is>
       </c>
-      <c r="J366" t="inlineStr">
+      <c r="J367" t="inlineStr">
         <is>
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr">
+      <c r="K367" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="L366" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M366" s="2" t="n">
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M367" s="2" t="n">
         <v>14743.65</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>707427-56-CM26</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M368" s="2" t="n">
+        <v>2229.93</v>
       </c>
     </row>
   </sheetData>
